--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0003T0006Z000C1N44_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0003T0006Z000C1N44_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.80462431627664</v>
+        <v>4.680751451394953</v>
       </c>
       <c r="D2" t="n">
-        <v>28.5</v>
+        <v>4.631250000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>10.27044406538442</v>
+        <v>1.668947160624969</v>
       </c>
       <c r="F2" t="n">
-        <v>9.631023320820002</v>
+        <v>1.56504128963325</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>3.737910799926865</v>
+        <v>0.6074105049881156</v>
       </c>
       <c r="D3" t="n">
-        <v>29.63442954939284</v>
+        <v>4.815594801776337</v>
       </c>
       <c r="E3" t="n">
-        <v>10.27044406538442</v>
+        <v>1.668947160624969</v>
       </c>
       <c r="F3" t="n">
-        <v>9.631023320820002</v>
+        <v>1.56504128963325</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.77415578505887</v>
+        <v>5.488300315072067</v>
       </c>
       <c r="D4" t="n">
-        <v>33.39717836905964</v>
+        <v>5.427041484972191</v>
       </c>
       <c r="E4" t="n">
-        <v>10.27044406538442</v>
+        <v>1.668947160624969</v>
       </c>
       <c r="F4" t="n">
-        <v>9.631023320820002</v>
+        <v>1.56504128963325</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>41.83232634068441</v>
+        <v>6.797753030361217</v>
       </c>
       <c r="D5" t="n">
-        <v>42.94182110716778</v>
+        <v>6.978045929914764</v>
       </c>
       <c r="E5" t="n">
-        <v>10.27044406538442</v>
+        <v>1.668947160624969</v>
       </c>
       <c r="F5" t="n">
-        <v>9.631023320820002</v>
+        <v>1.56504128963325</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>23.64339916347161</v>
+        <v>3.842052364064136</v>
       </c>
       <c r="D6" t="n">
-        <v>24.19770075855611</v>
+        <v>3.932126373265368</v>
       </c>
       <c r="E6" t="n">
-        <v>10.27044406538442</v>
+        <v>1.668947160624969</v>
       </c>
       <c r="F6" t="n">
-        <v>9.631023320820002</v>
+        <v>1.56504128963325</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>13.22938351034724</v>
+        <v>2.149774820431426</v>
       </c>
       <c r="D7" t="n">
-        <v>30.12413151821326</v>
+        <v>4.895171371709655</v>
       </c>
       <c r="E7" t="n">
-        <v>10.27044406538442</v>
+        <v>1.668947160624969</v>
       </c>
       <c r="F7" t="n">
-        <v>9.631023320820002</v>
+        <v>1.56504128963325</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>17.11724276862369</v>
+        <v>2.78155194990135</v>
       </c>
       <c r="D8" t="n">
-        <v>31.32491021535417</v>
+        <v>5.090297909995052</v>
       </c>
       <c r="E8" t="n">
-        <v>10.27044406538442</v>
+        <v>1.668947160624969</v>
       </c>
       <c r="F8" t="n">
-        <v>9.631023320820002</v>
+        <v>1.56504128963325</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>18.19086456826388</v>
+        <v>2.95601549234288</v>
       </c>
       <c r="D9" t="n">
-        <v>17.8111466779876</v>
+        <v>2.894311335172986</v>
       </c>
       <c r="E9" t="n">
-        <v>10.27044406538442</v>
+        <v>1.668947160624969</v>
       </c>
       <c r="F9" t="n">
-        <v>9.631023320820002</v>
+        <v>1.56504128963325</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>17.99438078018527</v>
+        <v>2.924086876780106</v>
       </c>
       <c r="D10" t="n">
-        <v>19.80329721232971</v>
+        <v>3.218035797003578</v>
       </c>
       <c r="E10" t="n">
-        <v>10.27044406538442</v>
+        <v>1.668947160624969</v>
       </c>
       <c r="F10" t="n">
-        <v>9.631023320820002</v>
+        <v>1.56504128963325</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>25.39443866625793</v>
+        <v>4.126596283266913</v>
       </c>
       <c r="D11" t="n">
-        <v>27.35201996275273</v>
+        <v>4.444703243947318</v>
       </c>
       <c r="E11" t="n">
-        <v>10.27044406538442</v>
+        <v>1.668947160624969</v>
       </c>
       <c r="F11" t="n">
-        <v>9.631023320820002</v>
+        <v>1.56504128963325</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>23.11384866265244</v>
+        <v>3.756000407681022</v>
       </c>
       <c r="D12" t="n">
-        <v>40.38700042758199</v>
+        <v>6.562887569482073</v>
       </c>
       <c r="E12" t="n">
-        <v>10.27044406538442</v>
+        <v>1.668947160624969</v>
       </c>
       <c r="F12" t="n">
-        <v>9.631023320820002</v>
+        <v>1.56504128963325</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>16.25429190274671</v>
+        <v>2.641322434196341</v>
       </c>
       <c r="D13" t="n">
-        <v>12.7534309109353</v>
+        <v>2.072432523026987</v>
       </c>
       <c r="E13" t="n">
-        <v>10.27044406538442</v>
+        <v>1.668947160624969</v>
       </c>
       <c r="F13" t="n">
-        <v>9.631023320820002</v>
+        <v>1.56504128963325</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>31.97674352494684</v>
+        <v>5.196220822803861</v>
       </c>
       <c r="D14" t="n">
-        <v>32.09439174561683</v>
+        <v>5.215338658662735</v>
       </c>
       <c r="E14" t="n">
-        <v>10.27044406538442</v>
+        <v>1.668947160624969</v>
       </c>
       <c r="F14" t="n">
-        <v>9.631023320820002</v>
+        <v>1.56504128963325</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>3.624976938126223</v>
+        <v>0.5890587524455113</v>
       </c>
       <c r="D15" t="n">
-        <v>5.803561162457116</v>
+        <v>0.9430786888992813</v>
       </c>
       <c r="E15" t="n">
-        <v>10.27044406538442</v>
+        <v>1.668947160624969</v>
       </c>
       <c r="F15" t="n">
-        <v>9.631023320820002</v>
+        <v>1.56504128963325</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>11.41784094920674</v>
+        <v>1.855399154246095</v>
       </c>
       <c r="D16" t="n">
-        <v>12.69928072423209</v>
+        <v>2.063633117687715</v>
       </c>
       <c r="E16" t="n">
-        <v>10.27044406538442</v>
+        <v>1.668947160624969</v>
       </c>
       <c r="F16" t="n">
-        <v>9.631023320820002</v>
+        <v>1.56504128963325</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>6.8819262589546</v>
+        <v>1.118313017080123</v>
       </c>
       <c r="D17" t="n">
-        <v>20.33838735003343</v>
+        <v>3.304987944380433</v>
       </c>
       <c r="E17" t="n">
-        <v>10.27044406538442</v>
+        <v>1.668947160624969</v>
       </c>
       <c r="F17" t="n">
-        <v>9.631023320820002</v>
+        <v>1.56504128963325</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>19.05596734247504</v>
+        <v>3.096594693152194</v>
       </c>
       <c r="D18" t="n">
-        <v>20.29376261769881</v>
+        <v>3.297736425376056</v>
       </c>
       <c r="E18" t="n">
-        <v>10.27044406538442</v>
+        <v>1.668947160624969</v>
       </c>
       <c r="F18" t="n">
-        <v>9.631023320820002</v>
+        <v>1.56504128963325</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
